--- a/filer_2/62725214_nkt_a_s.xlsx
+++ b/filer_2/62725214_nkt_a_s.xlsx
@@ -6699,20 +6699,20 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>SUM(B5:B8)</f>
+        <f>IF(COUNT('res_raw'!$F$2,'res_raw'!$F$3,'res_raw'!$F$4,'res_raw'!$F$5)=0,'res_raw'!$F$6,SUM(B5:B8))</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>SUM(C5:C8)</f>
+        <f>IF(COUNT('res_raw'!$E$2,'res_raw'!$E$3,'res_raw'!$E$4,'res_raw'!$E$5)=0,'res_raw'!$E$6,SUM(C5:C8))</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>SUM(D5:D8)</f>
+        <f>IF(COUNT('res_raw'!$D$2,'res_raw'!$D$3,'res_raw'!$D$4,'res_raw'!$D$5)=0,'res_raw'!$D$6,SUM(D5:D8))</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk.</t>
+          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk. Er komponenterne ikke indberettet, vises rapporteret bruttoresultat (fsa:GrossResult) direkte.</t>
         </is>
       </c>
     </row>

--- a/filer_2/62725214_nkt_a_s.xlsx
+++ b/filer_2/62725214_nkt_a_s.xlsx
@@ -649,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nkt (CVR None) — Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
+          <t>nkt — Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>nkt (CVR None) — Resultatopgørelse &amp; nøgleoplysninger (t.EUR)</t>
+          <t>nkt — Resultatopgørelse &amp; nøgleoplysninger (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -5372,7 +5372,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>nkt (CVR None) — Balance (t.EUR)</t>
+          <t>nkt — Balance (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -6444,7 +6444,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>nkt (CVR None) — Pengestrømsopgørelse (t.EUR)</t>
+          <t>nkt — Pengestrømsopgørelse (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -6560,7 +6560,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>nkt (CVR None) — Regnskabs- og nøgletal — artsopdelt</t>
+          <t>nkt — Regnskabs- og nøgletal — artsopdelt</t>
         </is>
       </c>
     </row>
@@ -6699,15 +6699,15 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>IF(COUNT('res_raw'!$F$2,'res_raw'!$F$3,'res_raw'!$F$4,'res_raw'!$F$5)=0,'res_raw'!$F$6,SUM(B5:B8))</f>
+        <f>IF(ABS((SUM(B5:B8))-'res_raw'!$F$6)&lt;=2,SUM(B5:B8),'res_raw'!$F$6)</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>IF(COUNT('res_raw'!$E$2,'res_raw'!$E$3,'res_raw'!$E$4,'res_raw'!$E$5)=0,'res_raw'!$E$6,SUM(C5:C8))</f>
+        <f>IF(ABS((SUM(C5:C8))-'res_raw'!$E$6)&lt;=2,SUM(C5:C8),'res_raw'!$E$6)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>IF(COUNT('res_raw'!$D$2,'res_raw'!$D$3,'res_raw'!$D$4,'res_raw'!$D$5)=0,'res_raw'!$D$6,SUM(D5:D8))</f>
+        <f>IF(ABS((SUM(D5:D8))-'res_raw'!$D$6)&lt;=2,SUM(D5:D8),'res_raw'!$D$6)</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -6795,15 +6795,15 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(B9:B12)</f>
+        <f>IF(ABS((SUM(B9:B12))-'res_raw'!$F$11)&lt;=2,SUM(B9:B12),'res_raw'!$F$11)</f>
         <v/>
       </c>
       <c r="C13" s="27">
-        <f>SUM(C9:C12)</f>
+        <f>IF(ABS((SUM(C9:C12))-'res_raw'!$E$11)&lt;=2,SUM(C9:C12),'res_raw'!$E$11)</f>
         <v/>
       </c>
       <c r="D13" s="27">
-        <f>SUM(D9:D12)</f>
+        <f>IF(ABS((SUM(D9:D12))-'res_raw'!$D$11)&lt;=2,SUM(D9:D12),'res_raw'!$D$11)</f>
         <v/>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -6867,15 +6867,15 @@
         </is>
       </c>
       <c r="B16" s="27">
-        <f>SUM(B13:B15)</f>
+        <f>IF(ABS((SUM(B13:B15))-'res_raw'!$F$16)&lt;=2,SUM(B13:B15),'res_raw'!$F$16)</f>
         <v/>
       </c>
       <c r="C16" s="27">
-        <f>SUM(C13:C15)</f>
+        <f>IF(ABS((SUM(C13:C15))-'res_raw'!$E$16)&lt;=2,SUM(C13:C15),'res_raw'!$E$16)</f>
         <v/>
       </c>
       <c r="D16" s="27">
-        <f>SUM(D13:D15)</f>
+        <f>IF(ABS((SUM(D13:D15))-'res_raw'!$D$16)&lt;=2,SUM(D13:D15),'res_raw'!$D$16)</f>
         <v/>
       </c>
       <c r="F16" s="28" t="inlineStr">
@@ -7786,7 +7786,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="33" t="inlineStr">
         <is>
-          <t>nkt (CVR None) — Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
+          <t>nkt — Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
         </is>
       </c>
     </row>

--- a/filer_2/62725214_nkt_a_s.xlsx
+++ b/filer_2/62725214_nkt_a_s.xlsx
@@ -5241,11 +5241,21 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
+      <c r="B15" s="17" t="n">
+        <v>-8200</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>9100</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>-15600</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>37000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
